--- a/data/source/material_workbench_tutorial_v2.xlsx
+++ b/data/source/material_workbench_tutorial_v2.xlsx
@@ -3522,6 +3522,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ME-01</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>HR-01</t>
@@ -3534,6 +3539,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ME-01</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>HR-01</t>
@@ -3546,6 +3556,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ME-01</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>HR-02</t>
@@ -3558,6 +3573,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ME-01</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>HR-02</t>
@@ -3570,6 +3590,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ME-02</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>HR-03</t>
@@ -3582,6 +3607,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ME-02</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>HR-03</t>
@@ -3594,6 +3624,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ME-03</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>HR-04</t>
@@ -3606,6 +3641,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ME-03</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>HR-04</t>
@@ -3618,6 +3658,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ME-03</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>HR-05</t>
@@ -3630,6 +3675,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ME-03</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>HR-05</t>
@@ -3642,6 +3692,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ME-04</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>HR-06</t>
@@ -3654,6 +3709,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ME-04</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>HR-06</t>
@@ -3666,6 +3726,21 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ME-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HR-01</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CR-01</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
           <t>AN-01</t>
@@ -3678,6 +3753,21 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ME-01</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HR-01</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CR-01</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
           <t>AN-01</t>
@@ -3690,6 +3780,21 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ME-01</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>HR-02</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CR-02</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
           <t>AN-02</t>
@@ -3702,6 +3807,21 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ME-01</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>HR-02</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CR-02</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
           <t>AN-02</t>
@@ -3714,6 +3834,21 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ME-02</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>HR-03</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CR-03</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
           <t>AN-03</t>
@@ -3726,6 +3861,21 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ME-02</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>HR-03</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CR-03</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
           <t>AN-03</t>
@@ -3738,6 +3888,21 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ME-03</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>HR-04</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CR-04</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
           <t>AN-04</t>
@@ -3750,6 +3915,21 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ME-03</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>HR-04</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CR-04</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
           <t>AN-04</t>
@@ -3762,6 +3942,21 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ME-03</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>HR-05</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CR-05</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
           <t>AN-05</t>
@@ -3774,6 +3969,21 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ME-03</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>HR-05</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CR-05</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>AN-05</t>
@@ -3786,6 +3996,21 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ME-04</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>HR-06</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CR-06</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
           <t>AN-06</t>
@@ -3798,6 +4023,21 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ME-04</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>HR-06</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CR-06</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>AN-06</t>
